--- a/data/historial/2026-07-01.xlsx
+++ b/data/historial/2026-07-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2A4778E-54F7-4153-B8A7-8960C58CF07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12D5A15-8F39-4EB2-92C4-D2FB982DEB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="283">
   <si>
     <t>GOMEZ MARTÍN</t>
   </si>
@@ -2759,7 +2759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -3783,188 +3783,6 @@
         <v>0</v>
       </c>
       <c r="H39" s="149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>230</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>2650.7972222207</v>
-      </c>
-      <c r="D40">
-        <v>13684.3941654091</v>
-      </c>
-      <c r="E40">
-        <v>40082800.76103171</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>140</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>4623.5154365081999</v>
-      </c>
-      <c r="D41">
-        <v>22058.482952382499</v>
-      </c>
-      <c r="E41">
-        <v>52746975.667182915</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>215</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42">
-        <v>714.68611111109999</v>
-      </c>
-      <c r="D42">
-        <v>8476.1750000004995</v>
-      </c>
-      <c r="E42">
-        <v>16480410.572651757</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43">
-        <v>1051.1805059507001</v>
-      </c>
-      <c r="D43">
-        <v>7110.5142830207997</v>
-      </c>
-      <c r="E43">
-        <v>31200035.617086809</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>146</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>1566.6459960326999</v>
-      </c>
-      <c r="D44">
-        <v>14396.834107144001</v>
-      </c>
-      <c r="E44">
-        <v>24332681.799774844</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>155</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>770.72769841410002</v>
-      </c>
-      <c r="D45">
-        <v>7497.0568488112003</v>
-      </c>
-      <c r="E45">
-        <v>18122843.629825346</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>228</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46">
-        <v>2968.9512222223002</v>
-      </c>
-      <c r="D46">
-        <v>1731.8200000003999</v>
-      </c>
-      <c r="E46">
-        <v>78320711.594213665</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
         <v>0</v>
       </c>
     </row>
@@ -11889,9 +11707,9 @@
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="1" bestFit="1" customWidth="1"/>
@@ -13679,36 +13497,36 @@
       </c>
       <c r="D43" s="4">
         <f>IFERROR(+VLOOKUP(B43,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>31200035.617086809</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4">
         <f t="shared" ref="F43" si="11">+D43-E43</f>
-        <v>31200035.617086809</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
         <f>+D43/C43</f>
-        <v>0.78000089042717025</v>
+        <v>0</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" ref="H43" si="12">+D43/$N$3*$N$4</f>
-        <v>811200926.04425704</v>
+        <v>0</v>
       </c>
       <c r="I43" s="5">
         <f>+H43/C43</f>
-        <v>20.280023151106427</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" ref="J43" si="13">+D43/$N$3</f>
-        <v>31200035.617086809</v>
+        <v>0</v>
       </c>
       <c r="K43" s="4">
         <f>+(C43-D43)/$N$2</f>
-        <v>351998.57531652763</v>
+        <v>1600000</v>
       </c>
       <c r="L43" s="4" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
-        <v>16224018.520885142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -13720,36 +13538,36 @@
       </c>
       <c r="D44" s="4">
         <f>IFERROR(+VLOOKUP(B44,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>24332681.799774844</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4">
         <f t="shared" ref="F44" si="14">+D44-E44</f>
-        <v>24332681.799774844</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
         <f>+D44/C44</f>
-        <v>0.81108939332582819</v>
+        <v>0</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" ref="H44" si="15">+D44/$N$3*$N$4</f>
-        <v>632649726.79414594</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5">
         <f>+H44/C44</f>
-        <v>21.088324226471531</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" ref="J44" si="16">+D44/$N$3</f>
-        <v>24332681.799774844</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4">
         <f>+(C44-D44)/$N$2</f>
-        <v>226692.72800900624</v>
+        <v>1200000</v>
       </c>
       <c r="L44" s="4" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
-        <v>12652994.53588292</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
